--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_04-06-2025.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_04-06-2025.xlsx
@@ -528,17 +528,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£11.25</t>
+          <t>£11.15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£11.25</t>
+          <t>£11.15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£11.25</t>
+          <t>£11.15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -615,17 +615,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£13.15</t>
+          <t>£12.80</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£13.15</t>
+          <t>£12.80</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£13.15</t>
+          <t>£12.80</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£16.73</t>
+          <t>£16.46</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£16.73</t>
+          <t>£16.46</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -789,17 +789,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£17.48</t>
+          <t>£16.70</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£17.48</t>
+          <t>£16.70</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£17.48</t>
+          <t>£16.70</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -876,17 +876,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£21.65</t>
+          <t>£21.20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£21.65</t>
+          <t>£21.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£21.65</t>
+          <t>£21.20</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -963,17 +963,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£23.44</t>
+          <t>£23.13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£23.44</t>
+          <t>£23.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£23.44</t>
+          <t>£23.13</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1224,17 +1224,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£29.36</t>
+          <t>£29.28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£29.36</t>
+          <t>£29.28</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£29.36</t>
+          <t>£29.28</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£31.62</t>
+          <t>Error: list index out of range</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£35.90</t>
+          <t>£35.85</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£35.90</t>
+          <t>£35.85</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
